--- a/StructureDefinition-openimis-claim-response.xlsx
+++ b/StructureDefinition-openimis-claim-response.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T15:39:34+00:00</t>
+    <t>2025-09-08T11:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -11798,7 +11798,7 @@
         <v>79</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>22</v>
@@ -12801,7 +12801,7 @@
         <v>79</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>22</v>
@@ -12912,7 +12912,7 @@
         <v>79</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>22</v>
@@ -13025,7 +13025,7 @@
         <v>79</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>22</v>
@@ -13794,7 +13794,7 @@
         <v>79</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>22</v>
@@ -14902,7 +14902,7 @@
         <v>79</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>22</v>
@@ -17681,7 +17681,7 @@
         <v>79</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>22</v>
@@ -18470,7 +18470,7 @@
         <v>22</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="L138" t="s" s="2">
         <v>560</v>
@@ -18579,7 +18579,7 @@
         <v>22</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="L139" t="s" s="2">
         <v>562</v>
@@ -19465,7 +19465,7 @@
         <v>22</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="L147" t="s" s="2">
         <v>578</v>
@@ -19574,7 +19574,7 @@
         <v>22</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="L148" t="s" s="2">
         <v>580</v>
@@ -19671,7 +19671,7 @@
         <v>79</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H149" t="s" s="2">
         <v>22</v>
@@ -22904,7 +22904,7 @@
         <v>22</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="L178" t="s" s="2">
         <v>704</v>
@@ -23013,7 +23013,7 @@
         <v>22</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="L179" t="s" s="2">
         <v>706</v>
@@ -24789,7 +24789,7 @@
         <v>22</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="L195" t="s" s="2">
         <v>726</v>
@@ -24898,7 +24898,7 @@
         <v>22</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="L196" t="s" s="2">
         <v>728</v>
@@ -26674,7 +26674,7 @@
         <v>22</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="L212" t="s" s="2">
         <v>747</v>
@@ -26783,7 +26783,7 @@
         <v>22</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="L213" t="s" s="2">
         <v>749</v>
@@ -26880,7 +26880,7 @@
         <v>79</v>
       </c>
       <c r="G214" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H214" t="s" s="2">
         <v>22</v>
@@ -26892,7 +26892,7 @@
         <v>22</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="L214" t="s" s="2">
         <v>751</v>
@@ -28103,7 +28103,7 @@
         <v>79</v>
       </c>
       <c r="G225" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H225" t="s" s="2">
         <v>22</v>
@@ -29217,7 +29217,7 @@
         <v>79</v>
       </c>
       <c r="G235" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H235" t="s" s="2">
         <v>22</v>
@@ -29330,7 +29330,7 @@
         <v>79</v>
       </c>
       <c r="G236" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H236" t="s" s="2">
         <v>22</v>
@@ -29443,7 +29443,7 @@
         <v>79</v>
       </c>
       <c r="G237" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H237" t="s" s="2">
         <v>22</v>
@@ -30000,7 +30000,7 @@
         <v>79</v>
       </c>
       <c r="G242" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H242" t="s" s="2">
         <v>22</v>
@@ -30111,7 +30111,7 @@
         <v>79</v>
       </c>
       <c r="G243" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H243" t="s" s="2">
         <v>22</v>
@@ -30333,7 +30333,7 @@
         <v>79</v>
       </c>
       <c r="G245" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H245" t="s" s="2">
         <v>22</v>
@@ -30559,7 +30559,7 @@
         <v>79</v>
       </c>
       <c r="G247" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H247" t="s" s="2">
         <v>22</v>
@@ -31564,7 +31564,7 @@
         <v>79</v>
       </c>
       <c r="G256" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H256" t="s" s="2">
         <v>22</v>

--- a/StructureDefinition-openimis-claim-response.xlsx
+++ b/StructureDefinition-openimis-claim-response.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:14:40+00:00</t>
+    <t>2025-09-08T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openimis-claim-response.xlsx
+++ b/StructureDefinition-openimis-claim-response.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:37:47+00:00</t>
+    <t>2025-09-08T11:49:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
